--- a/artfynd/A 47471-2025 artfynd.xlsx
+++ b/artfynd/A 47471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2278506</v>
+        <v>6761948</v>
       </c>
       <c r="B2" t="n">
-        <v>96224</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219769</v>
+        <v>49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Salepsrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Anacamptis pyramidalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byrum syd, Öl</t>
+          <t>Byrum, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619176.7240923785</v>
+        <v>619227</v>
       </c>
       <c r="R2" t="n">
-        <v>6344656.194367223</v>
+        <v>6344667</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,91 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Lennart Johnsson, Eva Bjelkendal, Ingrid Johnsson, Barbro Otterstedt, Elna Hultqvist</t>
+          <t>Via Helena Lager</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67082564</v>
+        <v>6741057</v>
       </c>
       <c r="B3" t="n">
-        <v>12834</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101192</v>
+        <v>374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattnosad rovfluga</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptarthrus vitripennis</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Meigen, 1820)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gamla landsvägen, Byrum, Öl</t>
+          <t>Byrum, vid sommarstuga 380 m SSV. största gården i byn jämte den lilla, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619173.8965311301</v>
+        <v>619262</v>
       </c>
       <c r="R3" t="n">
-        <v>6344678.859435822</v>
+        <v>6344702</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,27 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-11-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-11-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I toppen av solbelyst slånbuskage på obebyggd tomt vid gamla landsvägen.</t>
+          <t>Leg. Tommy Knutsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,94 +858,83 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>På mycket grova ekar (Quercus) av hagmarkstyp lämnad som vårdträd i trädgård vid</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>ToK 97-329</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>John Hallmén</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>John Hallmén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Tommy Knutsson - Import Fynddatabas 2013</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67082668</v>
+        <v>359040</v>
       </c>
       <c r="B4" t="n">
-        <v>53778</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102585</v>
+        <v>1348</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kvistkrabbspindel</t>
+          <t>Hjälmbrosklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pistius truncatus</t>
+          <t>Ramalina baltica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1772)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Lettau</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gamla landsvägen, Byrum, Öl</t>
+          <t>Byrum, vid sommarstuga 380 m SSV. största gården i byn jämte den lilla, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619173.8965311301</v>
+        <v>619262</v>
       </c>
       <c r="R4" t="n">
-        <v>6344678.859435822</v>
+        <v>6344702</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,27 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-07-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-11-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-11-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På ung hassel utmed gamla landsvägen.</t>
+          <t>Leg. Tommy Knutsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,71 +979,77 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På mycket grov ek (Quercus) av hagmarkstyp lämnad som vårdträd i trädgård vid ga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>John Hallmén</t>
+          <t>Tommy Knutsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>John Hallmén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Tommy Knutsson - Import Fynddatabas 2013</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101685002</v>
+        <v>115285800</v>
       </c>
       <c r="B5" t="n">
-        <v>96225</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219769</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bränsle, Öl</t>
+          <t>Böda, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619210.3186048502</v>
+        <v>619130</v>
       </c>
       <c r="R5" t="n">
-        <v>6344676.665640772</v>
+        <v>6344590</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,22 +1073,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,27 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103080035</v>
+        <v>67082564</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,41 +1121,54 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>101192</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Plattnosad rovfluga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leptarthrus vitripennis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Meigen, 1820)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Gamla landsvägen, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619316.6690056782</v>
+        <v>619174</v>
       </c>
       <c r="R6" t="n">
-        <v>6344639.672027811</v>
+        <v>6344679</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,29 +1190,19 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>832FB7B3-3ABD-460D-B736-5EF483227F31</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I toppen av solbelyst slånbuskage på obebyggd tomt vid gamla landsvägen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,53 +1217,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>John Hallmén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>John Hallmén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103081161</v>
+        <v>67082668</v>
       </c>
       <c r="B7" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>54733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>102585</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kvistkrabbspindel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pistius truncatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1772)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1345,19 +1262,40 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Gamla landsvägen, Byrum, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619265.3841433966</v>
+        <v>619174</v>
       </c>
       <c r="R7" t="n">
-        <v>6344574.274874288</v>
+        <v>6344679</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,29 +1317,19 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>BDC98510-A2AA-4756-8323-547521FD7A85</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På ung hassel utmed gamla landsvägen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,73 +1344,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>John Hallmén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>John Hallmén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103178799</v>
+        <v>2278506</v>
       </c>
       <c r="B8" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Byrum syd, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619257.3965705516</v>
+        <v>619177</v>
       </c>
       <c r="R8" t="n">
-        <v>6344681.280343734</v>
+        <v>6344656</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,29 +1419,14 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>613A1917-3829-4976-8E6A-1FE6B366F010</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,77 +1437,75 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Lennart Johnsson, Eva Bjelkendal, Ingrid Johnsson, Barbro Otterstedt, Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103178796</v>
+        <v>101685002</v>
       </c>
       <c r="B9" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>219769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Bränsle, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619304.1677577717</v>
+        <v>619210</v>
       </c>
       <c r="R9" t="n">
-        <v>6344677.762760374</v>
+        <v>6344677</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,29 +1527,14 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>9AAF391A-ED71-43A2-A5B2-C05A9521200F</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,31 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103178794</v>
+        <v>103080035</v>
       </c>
       <c r="B10" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619204.4131038588</v>
+        <v>619317</v>
       </c>
       <c r="R10" t="n">
-        <v>6344599.587258813</v>
+        <v>6344640</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1756,7 +1630,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0FDC5B15-EB5F-4706-AE12-259EE5FF3BEE</t>
+          <t>832FB7B3-3ABD-460D-B736-5EF483227F31</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1764,19 +1638,9 @@
           <t>2020-12-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1807,15 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103178797</v>
+        <v>103081161</v>
       </c>
       <c r="B11" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619274.7059806267</v>
+        <v>619266</v>
       </c>
       <c r="R11" t="n">
-        <v>6344627.080974143</v>
+        <v>6344574</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,7 +1740,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>57AC49FA-05B4-46DC-BAF4-7E238D5C7776</t>
+          <t>BDC98510-A2AA-4756-8323-547521FD7A85</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1889,19 +1748,9 @@
           <t>2020-12-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1770,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1932,15 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103178795</v>
+        <v>103178794</v>
       </c>
       <c r="B12" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1976,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619311.1065556587</v>
+        <v>619204</v>
       </c>
       <c r="R12" t="n">
-        <v>6344681.755258654</v>
+        <v>6344599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,7 +1850,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>509A527E-F25A-436F-8513-E7C1B5E56E44</t>
+          <t>0FDC5B15-EB5F-4706-AE12-259EE5FF3BEE</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2014,19 +1858,9 @@
           <t>2020-12-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,7 +1880,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2057,53 +1891,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6761948</v>
+        <v>103178795</v>
       </c>
       <c r="B13" t="n">
-        <v>96220</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Salepsrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anacamptis pyramidalis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Byrum, Öl</t>
+          <t>Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619227.4251911051</v>
+        <v>619311</v>
       </c>
       <c r="R13" t="n">
-        <v>6344666.87130674</v>
+        <v>6344682</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2125,24 +1958,19 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>509A527E-F25A-436F-8513-E7C1B5E56E44</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1995-01-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,15 +1985,455 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Helena Lager</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>103178796</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>619305</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6344677</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9AAF391A-ED71-43A2-A5B2-C05A9521200F</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103178797</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>619275</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6344627</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>57AC49FA-05B4-46DC-BAF4-7E238D5C7776</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103178799</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>619257</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6344681</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>613A1917-3829-4976-8E6A-1FE6B366F010</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-12-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115285799</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Böda, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>619129</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6344610</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47471-2025 artfynd.xlsx
+++ b/artfynd/A 47471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6761948</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/359040</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082564</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67082668</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2278506</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101685002</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103080035</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081161</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178794</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1998,6 +2058,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178795</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178796</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2218,6 +2288,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178797</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2328,6 +2403,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178799</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,8 +2514,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285799</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>